--- a/detailed_projection_report.xlsx
+++ b/detailed_projection_report.xlsx
@@ -199,19 +199,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>27</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>213</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>272</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>288</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>318</c:v>
+                <c:v>30</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>306</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>193</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>51</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>249</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -293,19 +293,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>30</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>231</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>295</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>312</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>345</c:v>
+                <c:v>31</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>310</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>196</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>52</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>253</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -901,10 +901,10 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>10</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>52</c:v>
+                <c:v>11</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>78</c:v>
               </c:pt>
               <c:pt idx="2">
                 <c:v>58</c:v>
@@ -913,7 +913,7 @@
                 <c:v>73</c:v>
               </c:pt>
               <c:pt idx="4">
-                <c:v>82</c:v>
+                <c:v>84</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -995,19 +995,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>21</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>106</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>118</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>148</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>166</c:v>
+                <c:v>11</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>78</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>58</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>73</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>84</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -1138,7 +1138,7 @@
                 <c:v>0</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>8</c:v>
+                <c:v>11</c:v>
               </c:pt>
               <c:pt idx="2">
                 <c:v>23</c:v>
@@ -1147,7 +1147,7 @@
                 <c:v>12</c:v>
               </c:pt>
               <c:pt idx="4">
-                <c:v>28</c:v>
+                <c:v>22</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -1232,16 +1232,16 @@
                 <c:v>49</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>36</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>103</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>54</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>125</c:v>
+                <c:v>23</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>47</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>25</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>45</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -1606,16 +1606,16 @@
                 <c:v>0</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>7</c:v>
-              </c:pt>
-              <c:pt idx="2">
+                <c:v>8</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>6</c:v>
+              </c:pt>
+              <c:pt idx="3">
                 <c:v>9</c:v>
               </c:pt>
-              <c:pt idx="3">
-                <c:v>14</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>15</c:v>
+              <c:pt idx="4">
+                <c:v>12</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -1703,13 +1703,13 @@
                 <c:v>16</c:v>
               </c:pt>
               <c:pt idx="2">
-                <c:v>21</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>32</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>34</c:v>
+                <c:v>12</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>18</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>24</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -1840,7 +1840,7 @@
                 <c:v>4</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>14</c:v>
+                <c:v>17</c:v>
               </c:pt>
               <c:pt idx="2">
                 <c:v>20</c:v>
@@ -1931,19 +1931,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>5</c:v>
-              </c:pt>
-              <c:pt idx="1">
+                <c:v>4</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>15</c:v>
+              </c:pt>
+              <c:pt idx="2">
                 <c:v>17</c:v>
               </c:pt>
-              <c:pt idx="2">
-                <c:v>24</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>26</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>29</c:v>
+              <c:pt idx="3">
+                <c:v>19</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>22</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -2074,7 +2074,7 @@
                 <c:v>3</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>14</c:v>
+                <c:v>33</c:v>
               </c:pt>
               <c:pt idx="2">
                 <c:v>33</c:v>
@@ -2165,19 +2165,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>2</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>6</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>13</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>7</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>14</c:v>
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>8</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>8</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>5</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>9</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -2642,7 +2642,7 @@
                 <c:v>2</c:v>
               </c:pt>
               <c:pt idx="3">
-                <c:v>2</c:v>
+                <c:v>1</c:v>
               </c:pt>
               <c:pt idx="4">
                 <c:v>2</c:v>
@@ -2773,19 +2773,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>7</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>56</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>82</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>90</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>145</c:v>
+                <c:v>11</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>110</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>81</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>88</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>143</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -2867,19 +2867,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>18</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>142</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>208</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>228</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>368</c:v>
+                <c:v>12</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>111</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>82</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>89</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>144</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -3241,19 +3241,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>14</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>119</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>108</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>132</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>104</c:v>
+                <c:v>12</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>103</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>85</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>90</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>113</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -3335,19 +3335,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>26</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>219</c:v>
-              </c:pt>
-              <c:pt idx="2">
+                <c:v>24</c:v>
+              </c:pt>
+              <c:pt idx="1">
                 <c:v>199</c:v>
               </c:pt>
-              <c:pt idx="3">
-                <c:v>243</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>192</c:v>
+              <c:pt idx="2">
+                <c:v>164</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>174</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>218</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -3487,7 +3487,7 @@
                 <c:v>1</c:v>
               </c:pt>
               <c:pt idx="4">
-                <c:v>1</c:v>
+                <c:v>0</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -3709,19 +3709,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>8</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>29</c:v>
-              </c:pt>
-              <c:pt idx="2">
+                <c:v>11</c:v>
+              </c:pt>
+              <c:pt idx="1">
                 <c:v>45</c:v>
               </c:pt>
-              <c:pt idx="3">
-                <c:v>36</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>54</c:v>
+              <c:pt idx="2">
+                <c:v>46</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>39</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>57</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -3803,19 +3803,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>19</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>67</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>104</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>83</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>125</c:v>
+                <c:v>14</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>57</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>58</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>49</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>72</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -3943,10 +3943,10 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>6</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>13</c:v>
+                <c:v>7</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>15</c:v>
               </c:pt>
               <c:pt idx="2">
                 <c:v>16</c:v>
@@ -4043,13 +4043,13 @@
                 <c:v>13</c:v>
               </c:pt>
               <c:pt idx="2">
-                <c:v>15</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>13</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>18</c:v>
+                <c:v>14</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>11</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>16</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -4180,16 +4180,16 @@
                 <c:v>0</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>12</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>23</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>21</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>40</c:v>
+                <c:v>25</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>22</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>19</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>44</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -4274,16 +4274,16 @@
                 <c:v>44</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>41</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>78</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>72</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>136</c:v>
+                <c:v>29</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>26</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>22</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>51</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -4411,19 +4411,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>14</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>72</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>100</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>101</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>127</c:v>
+                <c:v>21</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>114</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>110</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>111</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>129</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -4505,19 +4505,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>27</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>136</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>189</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>191</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>240</c:v>
+                <c:v>21</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>110</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>106</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>107</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>125</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -4645,13 +4645,13 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>9</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>35</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>49</c:v>
+                <c:v>11</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>46</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>51</c:v>
               </c:pt>
               <c:pt idx="3">
                 <c:v>46</c:v>
@@ -4739,19 +4739,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>21</c:v>
-              </c:pt>
-              <c:pt idx="1">
+                <c:v>17</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>71</c:v>
+              </c:pt>
+              <c:pt idx="2">
                 <c:v>79</c:v>
               </c:pt>
-              <c:pt idx="2">
-                <c:v>110</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>104</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>140</c:v>
+              <c:pt idx="3">
+                <c:v>71</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>96</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -4882,7 +4882,7 @@
                 <c:v>0</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>0</c:v>
+                <c:v>1</c:v>
               </c:pt>
               <c:pt idx="2">
                 <c:v>1</c:v>
@@ -5116,7 +5116,7 @@
                 <c:v>3</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>41</c:v>
+                <c:v>49</c:v>
               </c:pt>
               <c:pt idx="2">
                 <c:v>47</c:v>
@@ -5207,19 +5207,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>5</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>69</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>78</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>93</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>130</c:v>
+                <c:v>4</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>52</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>50</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>60</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>83</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -5815,19 +5815,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>14</c:v>
-              </c:pt>
-              <c:pt idx="1">
+                <c:v>19</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>34</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>21</c:v>
+              </c:pt>
+              <c:pt idx="3">
                 <c:v>26</c:v>
               </c:pt>
-              <c:pt idx="2">
-                <c:v>25</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>37</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>43</c:v>
+              <c:pt idx="4">
+                <c:v>36</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -5909,19 +5909,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>32</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>60</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>58</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>85</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>99</c:v>
+                <c:v>27</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>48</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>30</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>37</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>51</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -6283,10 +6283,10 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>13</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>7</c:v>
+                <c:v>19</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>23</c:v>
               </c:pt>
               <c:pt idx="2">
                 <c:v>28</c:v>
@@ -6380,16 +6380,16 @@
                 <c:v>4</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>2</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>8</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>4</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>8</c:v>
+                <c:v>5</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>6</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>3</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>5</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -6520,7 +6520,7 @@
                 <c:v>12</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>67</c:v>
+                <c:v>69</c:v>
               </c:pt>
               <c:pt idx="2">
                 <c:v>99</c:v>
@@ -6611,19 +6611,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>21</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>116</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>172</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>121</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>168</c:v>
+                <c:v>17</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>98</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>140</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>99</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>138</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -6751,19 +6751,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>3</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>22</c:v>
+                <c:v>4</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>50</c:v>
               </c:pt>
               <c:pt idx="2">
                 <c:v>33</c:v>
               </c:pt>
               <c:pt idx="3">
-                <c:v>37</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>56</c:v>
+                <c:v>16</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>45</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -6845,19 +6845,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>4</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>24</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>36</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>40</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>61</c:v>
+                <c:v>3</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>34</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>22</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>11</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>30</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -7219,19 +7219,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>20</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>116</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>148</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>160</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>207</c:v>
+                <c:v>28</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>178</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>142</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>150</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>208</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -7313,19 +7313,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>54</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>308</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>393</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>425</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>549</c:v>
+                <c:v>42</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>262</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>209</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>221</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>307</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -7453,19 +7453,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>7</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>59</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>52</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>73</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>79</c:v>
+                <c:v>6</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>71</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>49</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>74</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>74</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -7547,19 +7547,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>17</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>140</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>123</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>173</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>187</c:v>
+                <c:v>9</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>97</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>67</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>101</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>101</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -7687,19 +7687,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>18</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>23</c:v>
+                <c:v>19</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>42</c:v>
               </c:pt>
               <c:pt idx="2">
                 <c:v>33</c:v>
               </c:pt>
               <c:pt idx="3">
-                <c:v>37</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>44</c:v>
+                <c:v>11</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>36</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -7781,19 +7781,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>30</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>39</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>55</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>62</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>74</c:v>
+                <c:v>27</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>59</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>46</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>16</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>50</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -8389,10 +8389,10 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>9</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>25</c:v>
+                <c:v>10</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>27</c:v>
               </c:pt>
               <c:pt idx="2">
                 <c:v>24</c:v>
@@ -8483,19 +8483,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>8</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>22</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>21</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>28</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>32</c:v>
+                <c:v>9</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>23</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>20</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>27</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>31</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -8623,19 +8623,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>8</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>50</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>62</c:v>
+                <c:v>10</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>87</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>61</c:v>
               </c:pt>
               <c:pt idx="3">
                 <c:v>79</c:v>
               </c:pt>
               <c:pt idx="4">
-                <c:v>88</c:v>
+                <c:v>89</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -8717,19 +8717,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>13</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>81</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>101</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>128</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>143</c:v>
+                <c:v>8</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>66</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>47</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>60</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>68</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -8857,10 +8857,10 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>4</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>17</c:v>
+                <c:v>5</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>20</c:v>
               </c:pt>
               <c:pt idx="2">
                 <c:v>23</c:v>
@@ -8954,16 +8954,16 @@
                 <c:v>6</c:v>
               </c:pt>
               <c:pt idx="1">
+                <c:v>21</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>24</c:v>
+              </c:pt>
+              <c:pt idx="3">
                 <c:v>22</c:v>
               </c:pt>
-              <c:pt idx="2">
-                <c:v>30</c:v>
-              </c:pt>
-              <c:pt idx="3">
+              <c:pt idx="4">
                 <c:v>28</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>34</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -9559,10 +9559,10 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>2</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>20</c:v>
+                <c:v>3</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>36</c:v>
               </c:pt>
               <c:pt idx="2">
                 <c:v>28</c:v>
@@ -9571,7 +9571,7 @@
                 <c:v>70</c:v>
               </c:pt>
               <c:pt idx="4">
-                <c:v>75</c:v>
+                <c:v>56</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -9653,19 +9653,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>4</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>35</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>48</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>120</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>129</c:v>
+                <c:v>3</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>36</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>28</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>70</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>56</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -9793,16 +9793,16 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>7</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>42</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>53</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>57</c:v>
+                <c:v>9</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>65</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>55</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>60</c:v>
               </c:pt>
               <c:pt idx="4">
                 <c:v>70</c:v>
@@ -9887,19 +9887,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>18</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>104</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>131</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>141</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>173</c:v>
+                <c:v>12</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>86</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>73</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>80</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>93</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -10030,7 +10030,7 @@
                 <c:v>0</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>2</c:v>
+                <c:v>3</c:v>
               </c:pt>
               <c:pt idx="2">
                 <c:v>4</c:v>
@@ -10261,16 +10261,16 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>16</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>101</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>129</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>173</c:v>
+                <c:v>17</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>171</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>134</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>176</c:v>
               </c:pt>
               <c:pt idx="4">
                 <c:v>224</c:v>
@@ -10355,19 +10355,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>41</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>255</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>325</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>436</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>565</c:v>
+                <c:v>22</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>213</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>167</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>219</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>279</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -10495,10 +10495,10 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>32</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>117</c:v>
+                <c:v>33</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>116</c:v>
               </c:pt>
               <c:pt idx="2">
                 <c:v>119</c:v>
@@ -10589,19 +10589,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>44</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>161</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>163</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>176</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>192</c:v>
+                <c:v>42</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>145</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>149</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>160</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>175</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -10729,10 +10729,10 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>6</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>13</c:v>
+                <c:v>7</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>15</c:v>
               </c:pt>
               <c:pt idx="2">
                 <c:v>16</c:v>
@@ -10829,13 +10829,13 @@
                 <c:v>13</c:v>
               </c:pt>
               <c:pt idx="2">
-                <c:v>15</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>13</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>18</c:v>
+                <c:v>14</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>11</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>16</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -10963,19 +10963,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>7</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>24</c:v>
-              </c:pt>
-              <c:pt idx="2">
+                <c:v>9</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>36</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>35</c:v>
+              </c:pt>
+              <c:pt idx="3">
                 <c:v>34</c:v>
               </c:pt>
-              <c:pt idx="3">
-                <c:v>31</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>42</c:v>
+              <c:pt idx="4">
+                <c:v>46</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -11057,19 +11057,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>12</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>42</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>59</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>54</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>72</c:v>
+                <c:v>10</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>40</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>39</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>38</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>51</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -11665,10 +11665,10 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>14</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>44</c:v>
+                <c:v>13</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>37</c:v>
               </c:pt>
               <c:pt idx="2">
                 <c:v>48</c:v>
@@ -11759,19 +11759,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>33</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>104</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>113</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>123</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>135</c:v>
+                <c:v>29</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>83</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>107</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>116</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>127</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -11902,10 +11902,10 @@
                 <c:v>11</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>35</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>49</c:v>
+                <c:v>46</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>51</c:v>
               </c:pt>
               <c:pt idx="3">
                 <c:v>46</c:v>
@@ -11993,19 +11993,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>25</c:v>
-              </c:pt>
-              <c:pt idx="1">
+                <c:v>17</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>71</c:v>
+              </c:pt>
+              <c:pt idx="2">
                 <c:v>79</c:v>
               </c:pt>
-              <c:pt idx="2">
-                <c:v>110</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>104</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>140</c:v>
+              <c:pt idx="3">
+                <c:v>71</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>96</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -12133,19 +12133,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>8</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>9</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>22</c:v>
+                <c:v>14</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>25</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>23</c:v>
               </c:pt>
               <c:pt idx="3">
                 <c:v>17</c:v>
               </c:pt>
               <c:pt idx="4">
-                <c:v>33</c:v>
+                <c:v>34</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -12227,19 +12227,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>19</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>22</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>53</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>41</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>79</c:v>
+                <c:v>14</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>24</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>23</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>17</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>33</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -12367,16 +12367,16 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>7</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>36</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>44</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>56</c:v>
+                <c:v>11</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>63</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>45</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>55</c:v>
               </c:pt>
               <c:pt idx="4">
                 <c:v>74</c:v>
@@ -12461,19 +12461,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>19</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>96</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>117</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>149</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>196</c:v>
+                <c:v>13</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>70</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>50</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>62</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>83</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -12835,10 +12835,10 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>17</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>45</c:v>
+                <c:v>15</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>43</c:v>
               </c:pt>
               <c:pt idx="2">
                 <c:v>22</c:v>
@@ -12929,19 +12929,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>18</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>47</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>23</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>49</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>42</c:v>
+                <c:v>27</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>76</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>39</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>83</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>70</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -13081,7 +13081,7 @@
                 <c:v>1</c:v>
               </c:pt>
               <c:pt idx="4">
-                <c:v>4</c:v>
+                <c:v>3</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -13172,10 +13172,10 @@
                 <c:v>5</c:v>
               </c:pt>
               <c:pt idx="3">
-                <c:v>5</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>5</c:v>
+                <c:v>3</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>8</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -13306,7 +13306,7 @@
                 <c:v>3</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>16</c:v>
+                <c:v>18</c:v>
               </c:pt>
               <c:pt idx="2">
                 <c:v>14</c:v>
@@ -13397,19 +13397,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>5</c:v>
-              </c:pt>
-              <c:pt idx="1">
+                <c:v>6</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>32</c:v>
+              </c:pt>
+              <c:pt idx="2">
                 <c:v>25</c:v>
               </c:pt>
-              <c:pt idx="2">
-                <c:v>22</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>33</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>27</c:v>
+              <c:pt idx="3">
+                <c:v>38</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>31</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -13537,19 +13537,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>3</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>22</c:v>
+                <c:v>4</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>50</c:v>
               </c:pt>
               <c:pt idx="2">
                 <c:v>33</c:v>
               </c:pt>
               <c:pt idx="3">
-                <c:v>37</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>56</c:v>
+                <c:v>16</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>45</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -13631,19 +13631,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>4</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>24</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>36</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>40</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>61</c:v>
+                <c:v>3</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>34</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>22</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>11</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>30</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -13771,19 +13771,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>7</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>59</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>52</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>73</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>79</c:v>
+                <c:v>6</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>71</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>49</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>74</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>74</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -13865,19 +13865,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>17</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>140</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>123</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>173</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>187</c:v>
+                <c:v>9</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>97</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>67</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>101</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>101</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -14011,13 +14011,13 @@
                 <c:v>2</c:v>
               </c:pt>
               <c:pt idx="2">
-                <c:v>10</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>25</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>33</c:v>
+                <c:v>8</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>23</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>32</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -14099,19 +14099,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>13</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>25</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>125</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>313</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>413</c:v>
+                <c:v>4</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>7</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>27</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>77</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>107</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -14242,7 +14242,7 @@
                 <c:v>12</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>67</c:v>
+                <c:v>69</c:v>
               </c:pt>
               <c:pt idx="2">
                 <c:v>99</c:v>
@@ -14333,19 +14333,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>21</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>116</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>172</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>121</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>168</c:v>
+                <c:v>17</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>98</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>140</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>99</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>138</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -14707,19 +14707,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>18</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>82</c:v>
+                <c:v>26</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>147</c:v>
               </c:pt>
               <c:pt idx="2">
                 <c:v>123</c:v>
               </c:pt>
               <c:pt idx="3">
-                <c:v>118</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>175</c:v>
+                <c:v>114</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>176</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -14801,19 +14801,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>45</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>205</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>307</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>295</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>437</c:v>
+                <c:v>32</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>179</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>150</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>139</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>214</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -15409,10 +15409,10 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>4</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>17</c:v>
+                <c:v>5</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>20</c:v>
               </c:pt>
               <c:pt idx="2">
                 <c:v>23</c:v>
@@ -15506,16 +15506,16 @@
                 <c:v>6</c:v>
               </c:pt>
               <c:pt idx="1">
+                <c:v>21</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>24</c:v>
+              </c:pt>
+              <c:pt idx="3">
                 <c:v>22</c:v>
               </c:pt>
-              <c:pt idx="2">
-                <c:v>30</c:v>
-              </c:pt>
-              <c:pt idx="3">
+              <c:pt idx="4">
                 <c:v>28</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>34</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -15646,7 +15646,7 @@
                 <c:v>0</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>0</c:v>
+                <c:v>1</c:v>
               </c:pt>
               <c:pt idx="2">
                 <c:v>0</c:v>
@@ -15740,16 +15740,16 @@
                 <c:v>2</c:v>
               </c:pt>
               <c:pt idx="1">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="2">
                 <c:v>2</c:v>
               </c:pt>
-              <c:pt idx="2">
+              <c:pt idx="3">
                 <c:v>2</c:v>
               </c:pt>
-              <c:pt idx="3">
-                <c:v>2</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>4</c:v>
+              <c:pt idx="4">
+                <c:v>1</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -15974,16 +15974,16 @@
                 <c:v>4</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>4</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>4</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>4</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>8</c:v>
+                <c:v>2</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>2</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>2</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>3</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -16111,10 +16111,10 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>25</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>33</c:v>
+                <c:v>26</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>29</c:v>
               </c:pt>
               <c:pt idx="2">
                 <c:v>38</c:v>
@@ -16205,19 +16205,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>34</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>45</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>52</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>49</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>51</c:v>
+                <c:v>38</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>42</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>56</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>53</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>54</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -16345,10 +16345,10 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>15</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>31</c:v>
+                <c:v>16</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>30</c:v>
               </c:pt>
               <c:pt idx="2">
                 <c:v>28</c:v>
@@ -16442,16 +16442,16 @@
                 <c:v>24</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>50</c:v>
-              </c:pt>
-              <c:pt idx="2">
                 <c:v>45</c:v>
               </c:pt>
-              <c:pt idx="3">
-                <c:v>63</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>64</c:v>
+              <c:pt idx="2">
+                <c:v>42</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>58</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>60</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -16579,19 +16579,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>1</c:v>
-              </c:pt>
-              <c:pt idx="1">
+                <c:v>0</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>9</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>5</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>8</c:v>
+              </c:pt>
+              <c:pt idx="4">
                 <c:v>10</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>7</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>11</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>9</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -16673,19 +16673,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>1</c:v>
-              </c:pt>
-              <c:pt idx="1">
                 <c:v>6</c:v>
               </c:pt>
-              <c:pt idx="2">
-                <c:v>5</c:v>
-              </c:pt>
-              <c:pt idx="3">
+              <c:pt idx="1">
                 <c:v>7</c:v>
               </c:pt>
-              <c:pt idx="4">
+              <c:pt idx="2">
+                <c:v>4</c:v>
+              </c:pt>
+              <c:pt idx="3">
                 <c:v>6</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>8</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -16816,7 +16816,7 @@
                 <c:v>0</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>0</c:v>
+                <c:v>2</c:v>
               </c:pt>
               <c:pt idx="2">
                 <c:v>1</c:v>
@@ -17047,10 +17047,10 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>27</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>46</c:v>
+                <c:v>29</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>34</c:v>
               </c:pt>
               <c:pt idx="2">
                 <c:v>40</c:v>
@@ -17141,19 +17141,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>25</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>42</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>37</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>42</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>31</c:v>
+                <c:v>29</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>33</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>39</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>44</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>32</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -17281,13 +17281,13 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>7</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>57</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>68</c:v>
+                <c:v>9</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>86</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>70</c:v>
               </c:pt>
               <c:pt idx="3">
                 <c:v>74</c:v>
@@ -17375,19 +17375,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>16</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>125</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>149</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>162</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>177</c:v>
+                <c:v>11</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>103</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>84</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>88</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>97</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -17752,16 +17752,16 @@
                 <c:v>6</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>37</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>64</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>64</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>87</c:v>
+                <c:v>62</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>47</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>44</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>69</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -17843,19 +17843,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>6</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>34</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>58</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>58</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>79</c:v>
+                <c:v>4</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>39</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>30</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>28</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>44</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -18688,16 +18688,16 @@
                 <c:v>5</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>126</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>193</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>230</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>283</c:v>
+                <c:v>140</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>131</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>141</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>228</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -18779,19 +18779,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>12</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>295</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>451</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>538</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>661</c:v>
+                <c:v>9</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>226</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>212</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>228</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>368</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -18919,19 +18919,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>7</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>41</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>43</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>52</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>60</c:v>
+                <c:v>9</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>68</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>47</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>58</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>67</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -19013,19 +19013,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>17</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>99</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>104</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>125</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>144</c:v>
+                <c:v>9</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>65</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>45</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>55</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>64</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -19153,16 +19153,16 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>6</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>29</c:v>
+                <c:v>8</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>53</c:v>
               </c:pt>
               <c:pt idx="2">
                 <c:v>46</c:v>
               </c:pt>
               <c:pt idx="3">
-                <c:v>45</c:v>
+                <c:v>47</c:v>
               </c:pt>
               <c:pt idx="4">
                 <c:v>63</c:v>
@@ -19247,19 +19247,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>14</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>66</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>105</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>103</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>144</c:v>
+                <c:v>9</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>55</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>48</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>49</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>65</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -19621,10 +19621,10 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>21</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>51</c:v>
+                <c:v>17</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>33</c:v>
               </c:pt>
               <c:pt idx="2">
                 <c:v>49</c:v>
@@ -19715,19 +19715,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>61</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>146</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>141</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>164</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>144</c:v>
+                <c:v>71</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>137</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>204</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>237</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>208</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -20560,7 +20560,7 @@
                 <c:v>3</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>16</c:v>
+                <c:v>18</c:v>
               </c:pt>
               <c:pt idx="2">
                 <c:v>14</c:v>
@@ -20651,19 +20651,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>5</c:v>
-              </c:pt>
-              <c:pt idx="1">
+                <c:v>6</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>32</c:v>
+              </c:pt>
+              <c:pt idx="2">
                 <c:v>25</c:v>
               </c:pt>
-              <c:pt idx="2">
-                <c:v>22</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>33</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>27</c:v>
+              <c:pt idx="3">
+                <c:v>38</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>31</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -21025,10 +21025,10 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>3</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>29</c:v>
+                <c:v>4</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>33</c:v>
               </c:pt>
               <c:pt idx="2">
                 <c:v>46</c:v>
@@ -21119,19 +21119,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>6</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>52</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>82</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>89</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>101</c:v>
+                <c:v>5</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>40</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>56</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>60</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>69</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -21262,7 +21262,7 @@
                 <c:v>5</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>35</c:v>
+                <c:v>40</c:v>
               </c:pt>
               <c:pt idx="2">
                 <c:v>40</c:v>
@@ -21353,19 +21353,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>6</c:v>
+                <c:v>5</c:v>
               </c:pt>
               <c:pt idx="1">
                 <c:v>40</c:v>
               </c:pt>
               <c:pt idx="2">
-                <c:v>45</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>50</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>54</c:v>
+                <c:v>40</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>44</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>47</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -21727,10 +21727,10 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>15</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>31</c:v>
+                <c:v>16</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>30</c:v>
               </c:pt>
               <c:pt idx="2">
                 <c:v>28</c:v>
@@ -21824,16 +21824,16 @@
                 <c:v>24</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>50</c:v>
-              </c:pt>
-              <c:pt idx="2">
                 <c:v>45</c:v>
               </c:pt>
-              <c:pt idx="3">
-                <c:v>63</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>64</c:v>
+              <c:pt idx="2">
+                <c:v>42</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>58</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>60</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -21964,7 +21964,7 @@
                 <c:v>4</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>14</c:v>
+                <c:v>17</c:v>
               </c:pt>
               <c:pt idx="2">
                 <c:v>20</c:v>
@@ -22055,19 +22055,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>5</c:v>
-              </c:pt>
-              <c:pt idx="1">
+                <c:v>4</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>15</c:v>
+              </c:pt>
+              <c:pt idx="2">
                 <c:v>17</c:v>
               </c:pt>
-              <c:pt idx="2">
-                <c:v>24</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>26</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>29</c:v>
+              <c:pt idx="3">
+                <c:v>19</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>22</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -22198,7 +22198,7 @@
                 <c:v>3</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>14</c:v>
+                <c:v>33</c:v>
               </c:pt>
               <c:pt idx="2">
                 <c:v>33</c:v>
@@ -22289,19 +22289,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>2</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>6</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>13</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>7</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>14</c:v>
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>8</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>8</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>5</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>9</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -22429,10 +22429,10 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>14</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>44</c:v>
+                <c:v>13</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>37</c:v>
               </c:pt>
               <c:pt idx="2">
                 <c:v>48</c:v>
@@ -22523,19 +22523,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>33</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>104</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>113</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>123</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>135</c:v>
+                <c:v>29</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>83</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>107</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>116</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>127</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -22663,10 +22663,10 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>25</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>33</c:v>
+                <c:v>26</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>29</c:v>
               </c:pt>
               <c:pt idx="2">
                 <c:v>38</c:v>
@@ -22757,19 +22757,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>34</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>45</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>52</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>49</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>51</c:v>
+                <c:v>38</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>42</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>56</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>53</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>54</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -26549,13 +26549,13 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>27.0</v>
+        <v>30.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>279.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="3">
@@ -26563,13 +26563,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>213.0</v>
+        <v>306.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>231.0</v>
+        <v>310.0</v>
       </c>
     </row>
     <row r="4">
@@ -26577,13 +26577,13 @@
         <v>0.5</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>272.0</v>
+        <v>193.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>295.0</v>
+        <v>196.0</v>
       </c>
     </row>
     <row r="5">
@@ -26591,13 +26591,13 @@
         <v>0.75</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>288.0</v>
+        <v>51.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>312.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="6">
@@ -26605,13 +26605,13 @@
         <v>1.0</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>318.0</v>
+        <v>249.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>345.0</v>
+        <v>253.0</v>
       </c>
     </row>
   </sheetData>
@@ -26834,13 +26834,13 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>86.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>21.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="3">
@@ -26848,13 +26848,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>52.0</v>
+        <v>78.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>106.0</v>
+        <v>78.0</v>
       </c>
     </row>
     <row r="4">
@@ -26868,7 +26868,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>118.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="5">
@@ -26882,7 +26882,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>148.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="6">
@@ -26890,13 +26890,13 @@
         <v>1.0</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>82.0</v>
+        <v>84.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>166.0</v>
+        <v>84.0</v>
       </c>
     </row>
   </sheetData>
@@ -26943,13 +26943,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>36.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="4">
@@ -26963,7 +26963,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>103.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="5">
@@ -26977,7 +26977,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>54.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="6">
@@ -26985,13 +26985,13 @@
         <v>1.0</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>28.0</v>
+        <v>22.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>125.0</v>
+        <v>45.0</v>
       </c>
     </row>
   </sheetData>
@@ -27133,7 +27133,7 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
@@ -27147,13 +27147,13 @@
         <v>0.5</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>21.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="5">
@@ -27161,13 +27161,13 @@
         <v>0.75</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>32.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="6">
@@ -27175,13 +27175,13 @@
         <v>1.0</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>15.0</v>
+        <v>12.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>34.0</v>
+        <v>24.0</v>
       </c>
     </row>
   </sheetData>
@@ -27220,7 +27220,7 @@
         <v>21.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="3">
@@ -27228,13 +27228,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="4">
@@ -27248,7 +27248,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>24.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="5">
@@ -27262,7 +27262,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>26.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="6">
@@ -27276,7 +27276,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>29.0</v>
+        <v>22.0</v>
       </c>
     </row>
   </sheetData>
@@ -27315,7 +27315,7 @@
         <v>15.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="3">
@@ -27323,13 +27323,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>14.0</v>
+        <v>33.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="4">
@@ -27343,7 +27343,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>13.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="5">
@@ -27357,7 +27357,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="6">
@@ -27371,7 +27371,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
     </row>
   </sheetData>
@@ -27547,7 +27547,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="6">
@@ -27594,13 +27594,13 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>156.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>18.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="3">
@@ -27608,13 +27608,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>56.0</v>
+        <v>110.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>142.0</v>
+        <v>111.0</v>
       </c>
     </row>
     <row r="4">
@@ -27622,13 +27622,13 @@
         <v>0.5</v>
       </c>
       <c r="B4" t="n" s="0">
+        <v>81.0</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D4" t="n" s="0">
         <v>82.0</v>
-      </c>
-      <c r="C4" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D4" t="n" s="0">
-        <v>208.0</v>
       </c>
     </row>
     <row r="5">
@@ -27636,13 +27636,13 @@
         <v>0.75</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>90.0</v>
+        <v>88.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>228.0</v>
+        <v>89.0</v>
       </c>
     </row>
     <row r="6">
@@ -27650,13 +27650,13 @@
         <v>1.0</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>145.0</v>
+        <v>143.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>368.0</v>
+        <v>144.0</v>
       </c>
     </row>
   </sheetData>
@@ -27784,13 +27784,13 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>14.0</v>
+        <v>12.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>158.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="3">
@@ -27798,13 +27798,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>119.0</v>
+        <v>103.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>219.0</v>
+        <v>199.0</v>
       </c>
     </row>
     <row r="4">
@@ -27812,13 +27812,13 @@
         <v>0.5</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>108.0</v>
+        <v>85.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>199.0</v>
+        <v>164.0</v>
       </c>
     </row>
     <row r="5">
@@ -27826,13 +27826,13 @@
         <v>0.75</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>132.0</v>
+        <v>90.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>243.0</v>
+        <v>174.0</v>
       </c>
     </row>
     <row r="6">
@@ -27840,13 +27840,13 @@
         <v>1.0</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>104.0</v>
+        <v>113.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>192.0</v>
+        <v>218.0</v>
       </c>
     </row>
   </sheetData>
@@ -27935,7 +27935,7 @@
         <v>1.0</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>0.0</v>
@@ -27974,13 +27974,13 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>69.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>19.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="3">
@@ -27988,13 +27988,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>29.0</v>
+        <v>45.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>67.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="4">
@@ -28002,13 +28002,13 @@
         <v>0.5</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>45.0</v>
+        <v>46.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>104.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="5">
@@ -28016,13 +28016,13 @@
         <v>0.75</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>36.0</v>
+        <v>39.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>83.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="6">
@@ -28030,13 +28030,13 @@
         <v>1.0</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>54.0</v>
+        <v>57.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>125.0</v>
+        <v>72.0</v>
       </c>
     </row>
   </sheetData>
@@ -28069,7 +28069,7 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>14.0</v>
@@ -28083,7 +28083,7 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
@@ -28103,7 +28103,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="5">
@@ -28117,7 +28117,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="6">
@@ -28131,7 +28131,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>18.0</v>
+        <v>16.0</v>
       </c>
     </row>
   </sheetData>
@@ -28178,13 +28178,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>12.0</v>
+        <v>25.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>41.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="4">
@@ -28192,13 +28192,13 @@
         <v>0.5</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>78.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="5">
@@ -28206,13 +28206,13 @@
         <v>0.75</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>72.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="6">
@@ -28220,13 +28220,13 @@
         <v>1.0</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>40.0</v>
+        <v>44.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>136.0</v>
+        <v>51.0</v>
       </c>
     </row>
   </sheetData>
@@ -28259,13 +28259,13 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>14.0</v>
+        <v>21.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>128.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>27.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="3">
@@ -28273,13 +28273,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>72.0</v>
+        <v>114.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>136.0</v>
+        <v>110.0</v>
       </c>
     </row>
     <row r="4">
@@ -28287,13 +28287,13 @@
         <v>0.5</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>100.0</v>
+        <v>110.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>189.0</v>
+        <v>106.0</v>
       </c>
     </row>
     <row r="5">
@@ -28301,13 +28301,13 @@
         <v>0.75</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>101.0</v>
+        <v>111.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>191.0</v>
+        <v>107.0</v>
       </c>
     </row>
     <row r="6">
@@ -28315,13 +28315,13 @@
         <v>1.0</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>127.0</v>
+        <v>129.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>240.0</v>
+        <v>125.0</v>
       </c>
     </row>
   </sheetData>
@@ -28354,13 +28354,13 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>83.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>21.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="3">
@@ -28368,13 +28368,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>35.0</v>
+        <v>46.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>79.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="4">
@@ -28382,13 +28382,13 @@
         <v>0.5</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>49.0</v>
+        <v>51.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>110.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="5">
@@ -28402,7 +28402,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>104.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="6">
@@ -28416,7 +28416,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>140.0</v>
+        <v>96.0</v>
       </c>
     </row>
   </sheetData>
@@ -28463,7 +28463,7 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
@@ -28550,7 +28550,7 @@
         <v>70.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="3">
@@ -28558,13 +28558,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>41.0</v>
+        <v>49.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>69.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="4">
@@ -28578,7 +28578,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>78.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="5">
@@ -28592,7 +28592,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>93.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="6">
@@ -28606,7 +28606,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>130.0</v>
+        <v>83.0</v>
       </c>
     </row>
   </sheetData>
@@ -28829,13 +28829,13 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>14.0</v>
+        <v>19.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>47.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>32.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="3">
@@ -28843,13 +28843,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>26.0</v>
+        <v>34.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>60.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="4">
@@ -28857,13 +28857,13 @@
         <v>0.5</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>25.0</v>
+        <v>21.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>58.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="5">
@@ -28871,13 +28871,13 @@
         <v>0.75</v>
       </c>
       <c r="B5" t="n" s="0">
+        <v>26.0</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D5" t="n" s="0">
         <v>37.0</v>
-      </c>
-      <c r="C5" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D5" t="n" s="0">
-        <v>85.0</v>
       </c>
     </row>
     <row r="6">
@@ -28885,13 +28885,13 @@
         <v>1.0</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>43.0</v>
+        <v>36.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>99.0</v>
+        <v>51.0</v>
       </c>
     </row>
   </sheetData>
@@ -29019,7 +29019,7 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>13.0</v>
+        <v>19.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>9.0</v>
@@ -29033,13 +29033,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>7.0</v>
+        <v>23.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="4">
@@ -29053,7 +29053,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="5">
@@ -29067,7 +29067,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="6">
@@ -29081,7 +29081,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
   </sheetData>
@@ -29120,7 +29120,7 @@
         <v>138.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>21.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="3">
@@ -29128,13 +29128,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>67.0</v>
+        <v>69.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>116.0</v>
+        <v>98.0</v>
       </c>
     </row>
     <row r="4">
@@ -29148,7 +29148,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>172.0</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="5">
@@ -29162,7 +29162,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>121.0</v>
+        <v>99.0</v>
       </c>
     </row>
     <row r="6">
@@ -29176,7 +29176,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>168.0</v>
+        <v>138.0</v>
       </c>
     </row>
   </sheetData>
@@ -29209,13 +29209,13 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>39.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="3">
@@ -29223,13 +29223,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>22.0</v>
+        <v>50.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>24.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="4">
@@ -29243,7 +29243,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>36.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="5">
@@ -29251,13 +29251,13 @@
         <v>0.75</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>37.0</v>
+        <v>16.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>40.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="6">
@@ -29265,13 +29265,13 @@
         <v>1.0</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>56.0</v>
+        <v>45.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>61.0</v>
+        <v>30.0</v>
       </c>
     </row>
   </sheetData>
@@ -29399,13 +29399,13 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>20.0</v>
+        <v>28.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>278.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>54.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="3">
@@ -29413,13 +29413,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>116.0</v>
+        <v>178.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>308.0</v>
+        <v>262.0</v>
       </c>
     </row>
     <row r="4">
@@ -29427,13 +29427,13 @@
         <v>0.5</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>148.0</v>
+        <v>142.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>393.0</v>
+        <v>209.0</v>
       </c>
     </row>
     <row r="5">
@@ -29441,13 +29441,13 @@
         <v>0.75</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>160.0</v>
+        <v>150.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>425.0</v>
+        <v>221.0</v>
       </c>
     </row>
     <row r="6">
@@ -29455,13 +29455,13 @@
         <v>1.0</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>207.0</v>
+        <v>208.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>549.0</v>
+        <v>307.0</v>
       </c>
     </row>
   </sheetData>
@@ -29494,13 +29494,13 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>89.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>17.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="3">
@@ -29508,13 +29508,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>59.0</v>
+        <v>71.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>140.0</v>
+        <v>97.0</v>
       </c>
     </row>
     <row r="4">
@@ -29522,13 +29522,13 @@
         <v>0.5</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>52.0</v>
+        <v>49.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>123.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="5">
@@ -29536,13 +29536,13 @@
         <v>0.75</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>73.0</v>
+        <v>74.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>173.0</v>
+        <v>101.0</v>
       </c>
     </row>
     <row r="6">
@@ -29550,13 +29550,13 @@
         <v>1.0</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>79.0</v>
+        <v>74.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>187.0</v>
+        <v>101.0</v>
       </c>
     </row>
   </sheetData>
@@ -29589,13 +29589,13 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>49.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>30.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="3">
@@ -29603,13 +29603,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>23.0</v>
+        <v>42.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>39.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="4">
@@ -29623,7 +29623,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>55.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="5">
@@ -29631,13 +29631,13 @@
         <v>0.75</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>37.0</v>
+        <v>11.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>62.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="6">
@@ -29645,13 +29645,13 @@
         <v>1.0</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>44.0</v>
+        <v>36.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>74.0</v>
+        <v>50.0</v>
       </c>
     </row>
   </sheetData>
@@ -29874,13 +29874,13 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>21.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="3">
@@ -29888,13 +29888,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="4">
@@ -29908,7 +29908,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="5">
@@ -29922,7 +29922,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="6">
@@ -29936,7 +29936,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
     </row>
   </sheetData>
@@ -29969,13 +29969,13 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>77.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>13.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="3">
@@ -29983,13 +29983,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>50.0</v>
+        <v>87.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>81.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="4">
@@ -29997,13 +29997,13 @@
         <v>0.5</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>62.0</v>
+        <v>61.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>101.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="5">
@@ -30017,7 +30017,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>128.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="6">
@@ -30025,13 +30025,13 @@
         <v>1.0</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>88.0</v>
+        <v>89.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>143.0</v>
+        <v>68.0</v>
       </c>
     </row>
   </sheetData>
@@ -30064,7 +30064,7 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>27.0</v>
@@ -30078,13 +30078,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>17.0</v>
+        <v>20.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="4">
@@ -30098,7 +30098,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>30.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="5">
@@ -30112,7 +30112,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>28.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="6">
@@ -30126,7 +30126,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>34.0</v>
+        <v>28.0</v>
       </c>
     </row>
   </sheetData>
@@ -30349,13 +30349,13 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>60.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="3">
@@ -30363,13 +30363,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>20.0</v>
+        <v>36.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="4">
@@ -30383,7 +30383,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>48.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="5">
@@ -30397,7 +30397,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>120.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="6">
@@ -30405,13 +30405,13 @@
         <v>1.0</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>75.0</v>
+        <v>56.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>129.0</v>
+        <v>56.0</v>
       </c>
     </row>
   </sheetData>
@@ -30444,13 +30444,13 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>91.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>18.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="3">
@@ -30458,13 +30458,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>42.0</v>
+        <v>65.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>104.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="4">
@@ -30472,13 +30472,13 @@
         <v>0.5</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>53.0</v>
+        <v>55.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>131.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="5">
@@ -30486,13 +30486,13 @@
         <v>0.75</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>57.0</v>
+        <v>60.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>141.0</v>
+        <v>80.0</v>
       </c>
     </row>
     <row r="6">
@@ -30506,7 +30506,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>173.0</v>
+        <v>93.0</v>
       </c>
     </row>
   </sheetData>
@@ -30553,7 +30553,7 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
@@ -30634,13 +30634,13 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>260.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>41.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="3">
@@ -30648,13 +30648,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>101.0</v>
+        <v>171.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>255.0</v>
+        <v>213.0</v>
       </c>
     </row>
     <row r="4">
@@ -30662,13 +30662,13 @@
         <v>0.5</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>129.0</v>
+        <v>134.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>325.0</v>
+        <v>167.0</v>
       </c>
     </row>
     <row r="5">
@@ -30676,13 +30676,13 @@
         <v>0.75</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>173.0</v>
+        <v>176.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>436.0</v>
+        <v>219.0</v>
       </c>
     </row>
     <row r="6">
@@ -30696,7 +30696,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>565.0</v>
+        <v>279.0</v>
       </c>
     </row>
   </sheetData>
@@ -30729,13 +30729,13 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>152.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>44.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="3">
@@ -30743,13 +30743,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>117.0</v>
+        <v>116.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>161.0</v>
+        <v>145.0</v>
       </c>
     </row>
     <row r="4">
@@ -30763,7 +30763,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>163.0</v>
+        <v>149.0</v>
       </c>
     </row>
     <row r="5">
@@ -30777,7 +30777,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>176.0</v>
+        <v>160.0</v>
       </c>
     </row>
     <row r="6">
@@ -30791,7 +30791,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>192.0</v>
+        <v>175.0</v>
       </c>
     </row>
   </sheetData>
@@ -30824,7 +30824,7 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>14.0</v>
@@ -30838,7 +30838,7 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
@@ -30858,7 +30858,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="5">
@@ -30872,7 +30872,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="6">
@@ -30886,7 +30886,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>18.0</v>
+        <v>16.0</v>
       </c>
     </row>
   </sheetData>
@@ -30919,13 +30919,13 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>48.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="3">
@@ -30933,13 +30933,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>24.0</v>
+        <v>36.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>42.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="4">
@@ -30947,13 +30947,13 @@
         <v>0.5</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>59.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="5">
@@ -30961,13 +30961,13 @@
         <v>0.75</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>31.0</v>
+        <v>34.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>54.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="6">
@@ -30975,13 +30975,13 @@
         <v>1.0</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>42.0</v>
+        <v>46.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>72.0</v>
+        <v>51.0</v>
       </c>
     </row>
   </sheetData>
@@ -31204,13 +31204,13 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>79.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>33.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="3">
@@ -31218,13 +31218,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>44.0</v>
+        <v>37.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>104.0</v>
+        <v>83.0</v>
       </c>
     </row>
     <row r="4">
@@ -31238,7 +31238,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>113.0</v>
+        <v>107.0</v>
       </c>
     </row>
     <row r="5">
@@ -31252,7 +31252,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>123.0</v>
+        <v>116.0</v>
       </c>
     </row>
     <row r="6">
@@ -31266,7 +31266,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>135.0</v>
+        <v>127.0</v>
       </c>
     </row>
   </sheetData>
@@ -31305,7 +31305,7 @@
         <v>83.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>25.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="3">
@@ -31313,13 +31313,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>35.0</v>
+        <v>46.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>79.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="4">
@@ -31327,13 +31327,13 @@
         <v>0.5</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>49.0</v>
+        <v>51.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>110.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="5">
@@ -31347,7 +31347,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>104.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="6">
@@ -31361,7 +31361,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>140.0</v>
+        <v>96.0</v>
       </c>
     </row>
   </sheetData>
@@ -31394,13 +31394,13 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>8.0</v>
+        <v>14.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>44.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>19.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="3">
@@ -31408,13 +31408,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>9.0</v>
+        <v>25.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="4">
@@ -31422,13 +31422,13 @@
         <v>0.5</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>53.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="5">
@@ -31442,7 +31442,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>41.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="6">
@@ -31450,13 +31450,13 @@
         <v>1.0</v>
       </c>
       <c r="B6" t="n" s="0">
+        <v>34.0</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D6" t="n" s="0">
         <v>33.0</v>
-      </c>
-      <c r="C6" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D6" t="n" s="0">
-        <v>79.0</v>
       </c>
     </row>
   </sheetData>
@@ -31489,13 +31489,13 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>87.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>19.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="3">
@@ -31503,13 +31503,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>36.0</v>
+        <v>63.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>96.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="4">
@@ -31517,13 +31517,13 @@
         <v>0.5</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>44.0</v>
+        <v>45.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>117.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="5">
@@ -31531,13 +31531,13 @@
         <v>0.75</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>56.0</v>
+        <v>55.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>149.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="6">
@@ -31551,7 +31551,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>196.0</v>
+        <v>83.0</v>
       </c>
     </row>
   </sheetData>
@@ -31679,13 +31679,13 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>35.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>18.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="3">
@@ -31693,13 +31693,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>45.0</v>
+        <v>43.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>47.0</v>
+        <v>76.0</v>
       </c>
     </row>
     <row r="4">
@@ -31713,7 +31713,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>23.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="5">
@@ -31727,7 +31727,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>49.0</v>
+        <v>83.0</v>
       </c>
     </row>
     <row r="6">
@@ -31741,7 +31741,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>42.0</v>
+        <v>70.0</v>
       </c>
     </row>
   </sheetData>
@@ -31822,7 +31822,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="6">
@@ -31830,13 +31830,13 @@
         <v>1.0</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
   </sheetData>
@@ -31875,7 +31875,7 @@
         <v>22.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="3">
@@ -31883,13 +31883,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>25.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="4">
@@ -31903,7 +31903,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="5">
@@ -31917,7 +31917,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>33.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="6">
@@ -31931,7 +31931,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>27.0</v>
+        <v>31.0</v>
       </c>
     </row>
   </sheetData>
@@ -31964,13 +31964,13 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>39.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="3">
@@ -31978,13 +31978,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>22.0</v>
+        <v>50.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>24.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="4">
@@ -31998,7 +31998,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>36.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="5">
@@ -32006,13 +32006,13 @@
         <v>0.75</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>37.0</v>
+        <v>16.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>40.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="6">
@@ -32020,13 +32020,13 @@
         <v>1.0</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>56.0</v>
+        <v>45.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>61.0</v>
+        <v>30.0</v>
       </c>
     </row>
   </sheetData>
@@ -32059,13 +32059,13 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>89.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>17.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="3">
@@ -32073,13 +32073,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>59.0</v>
+        <v>71.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>140.0</v>
+        <v>97.0</v>
       </c>
     </row>
     <row r="4">
@@ -32087,13 +32087,13 @@
         <v>0.5</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>52.0</v>
+        <v>49.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>123.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="5">
@@ -32101,13 +32101,13 @@
         <v>0.75</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>73.0</v>
+        <v>74.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>173.0</v>
+        <v>101.0</v>
       </c>
     </row>
     <row r="6">
@@ -32115,13 +32115,13 @@
         <v>1.0</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>79.0</v>
+        <v>74.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>187.0</v>
+        <v>101.0</v>
       </c>
     </row>
   </sheetData>
@@ -32160,7 +32160,7 @@
         <v>49.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>13.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="3">
@@ -32174,7 +32174,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>25.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="4">
@@ -32182,13 +32182,13 @@
         <v>0.5</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>125.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="5">
@@ -32196,13 +32196,13 @@
         <v>0.75</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>25.0</v>
+        <v>23.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>313.0</v>
+        <v>77.0</v>
       </c>
     </row>
     <row r="6">
@@ -32210,13 +32210,13 @@
         <v>1.0</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>33.0</v>
+        <v>32.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>413.0</v>
+        <v>107.0</v>
       </c>
     </row>
   </sheetData>
@@ -32255,7 +32255,7 @@
         <v>138.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>21.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="3">
@@ -32263,13 +32263,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>67.0</v>
+        <v>69.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>116.0</v>
+        <v>98.0</v>
       </c>
     </row>
     <row r="4">
@@ -32283,7 +32283,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>172.0</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="5">
@@ -32297,7 +32297,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>121.0</v>
+        <v>99.0</v>
       </c>
     </row>
     <row r="6">
@@ -32311,7 +32311,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>168.0</v>
+        <v>138.0</v>
       </c>
     </row>
   </sheetData>
@@ -32439,13 +32439,13 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>18.0</v>
+        <v>26.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>230.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>45.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="3">
@@ -32453,13 +32453,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>82.0</v>
+        <v>147.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>205.0</v>
+        <v>179.0</v>
       </c>
     </row>
     <row r="4">
@@ -32473,7 +32473,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>307.0</v>
+        <v>150.0</v>
       </c>
     </row>
     <row r="5">
@@ -32481,13 +32481,13 @@
         <v>0.75</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>118.0</v>
+        <v>114.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>295.0</v>
+        <v>139.0</v>
       </c>
     </row>
     <row r="6">
@@ -32495,13 +32495,13 @@
         <v>1.0</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>175.0</v>
+        <v>176.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>437.0</v>
+        <v>214.0</v>
       </c>
     </row>
   </sheetData>
@@ -32724,7 +32724,7 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>27.0</v>
@@ -32738,13 +32738,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>17.0</v>
+        <v>20.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="4">
@@ -32758,7 +32758,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>30.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="5">
@@ -32772,7 +32772,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>28.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="6">
@@ -32786,7 +32786,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>34.0</v>
+        <v>28.0</v>
       </c>
     </row>
   </sheetData>
@@ -32833,13 +32833,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="4">
@@ -32881,7 +32881,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
   </sheetData>
@@ -32934,7 +32934,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="4">
@@ -32948,7 +32948,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="5">
@@ -32962,7 +32962,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="6">
@@ -32976,7 +32976,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
   </sheetData>
@@ -33009,13 +33009,13 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>42.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>34.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="3">
@@ -33023,13 +33023,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>33.0</v>
+        <v>29.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>45.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="4">
@@ -33043,7 +33043,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="5">
@@ -33057,7 +33057,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>49.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="6">
@@ -33071,7 +33071,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>51.0</v>
+        <v>54.0</v>
       </c>
     </row>
   </sheetData>
@@ -33104,7 +33104,7 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>40.0</v>
@@ -33118,13 +33118,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>50.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="4">
@@ -33138,7 +33138,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>45.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="5">
@@ -33152,7 +33152,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>63.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="6">
@@ -33166,7 +33166,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>64.0</v>
+        <v>60.0</v>
       </c>
     </row>
   </sheetData>
@@ -33199,13 +33199,13 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>6.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="3">
@@ -33213,13 +33213,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="4">
@@ -33227,13 +33227,13 @@
         <v>0.5</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="5">
@@ -33241,13 +33241,13 @@
         <v>0.75</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="6">
@@ -33255,13 +33255,13 @@
         <v>1.0</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
   </sheetData>
@@ -33308,7 +33308,7 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
@@ -33389,13 +33389,13 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>31.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>25.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="3">
@@ -33403,13 +33403,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>46.0</v>
+        <v>34.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>42.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="4">
@@ -33423,7 +33423,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>37.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="5">
@@ -33437,7 +33437,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>42.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="6">
@@ -33451,7 +33451,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
   </sheetData>
@@ -33484,13 +33484,13 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>16.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="3">
@@ -33498,13 +33498,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>57.0</v>
+        <v>86.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>125.0</v>
+        <v>103.0</v>
       </c>
     </row>
     <row r="4">
@@ -33512,13 +33512,13 @@
         <v>0.5</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>68.0</v>
+        <v>70.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>149.0</v>
+        <v>84.0</v>
       </c>
     </row>
     <row r="5">
@@ -33532,7 +33532,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>162.0</v>
+        <v>88.0</v>
       </c>
     </row>
     <row r="6">
@@ -33546,7 +33546,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>177.0</v>
+        <v>97.0</v>
       </c>
     </row>
   </sheetData>
@@ -33680,7 +33680,7 @@
         <v>63.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="3">
@@ -33688,13 +33688,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>37.0</v>
+        <v>62.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>34.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="4">
@@ -33702,13 +33702,13 @@
         <v>0.5</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>64.0</v>
+        <v>47.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>58.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="5">
@@ -33716,13 +33716,13 @@
         <v>0.75</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>64.0</v>
+        <v>44.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>58.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="6">
@@ -33730,13 +33730,13 @@
         <v>1.0</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>87.0</v>
+        <v>69.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>79.0</v>
+        <v>44.0</v>
       </c>
     </row>
   </sheetData>
@@ -34060,7 +34060,7 @@
         <v>321.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="3">
@@ -34068,13 +34068,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>126.0</v>
+        <v>140.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>295.0</v>
+        <v>226.0</v>
       </c>
     </row>
     <row r="4">
@@ -34082,13 +34082,13 @@
         <v>0.5</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>193.0</v>
+        <v>131.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>451.0</v>
+        <v>212.0</v>
       </c>
     </row>
     <row r="5">
@@ -34096,13 +34096,13 @@
         <v>0.75</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>230.0</v>
+        <v>141.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>538.0</v>
+        <v>228.0</v>
       </c>
     </row>
     <row r="6">
@@ -34110,13 +34110,13 @@
         <v>1.0</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>283.0</v>
+        <v>228.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>661.0</v>
+        <v>368.0</v>
       </c>
     </row>
   </sheetData>
@@ -34149,13 +34149,13 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>68.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>17.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="3">
@@ -34163,13 +34163,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>41.0</v>
+        <v>68.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>99.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="4">
@@ -34177,13 +34177,13 @@
         <v>0.5</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>43.0</v>
+        <v>47.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>104.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="5">
@@ -34191,13 +34191,13 @@
         <v>0.75</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>52.0</v>
+        <v>58.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>125.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="6">
@@ -34205,13 +34205,13 @@
         <v>1.0</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>60.0</v>
+        <v>67.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>144.0</v>
+        <v>64.0</v>
       </c>
     </row>
   </sheetData>
@@ -34244,13 +34244,13 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>72.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="3">
@@ -34258,13 +34258,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>29.0</v>
+        <v>53.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>66.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="4">
@@ -34278,7 +34278,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>105.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="5">
@@ -34286,13 +34286,13 @@
         <v>0.75</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>45.0</v>
+        <v>47.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>103.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="6">
@@ -34306,7 +34306,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>144.0</v>
+        <v>65.0</v>
       </c>
     </row>
   </sheetData>
@@ -34434,13 +34434,13 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>21.0</v>
+        <v>17.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>83.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>61.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="3">
@@ -34448,13 +34448,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>51.0</v>
+        <v>33.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>146.0</v>
+        <v>137.0</v>
       </c>
     </row>
     <row r="4">
@@ -34468,7 +34468,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>141.0</v>
+        <v>204.0</v>
       </c>
     </row>
     <row r="5">
@@ -34482,7 +34482,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>164.0</v>
+        <v>237.0</v>
       </c>
     </row>
     <row r="6">
@@ -34496,7 +34496,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>144.0</v>
+        <v>208.0</v>
       </c>
     </row>
   </sheetData>
@@ -34820,7 +34820,7 @@
         <v>22.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="3">
@@ -34828,13 +34828,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>25.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="4">
@@ -34848,7 +34848,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="5">
@@ -34862,7 +34862,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>33.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="6">
@@ -34876,7 +34876,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>27.0</v>
+        <v>31.0</v>
       </c>
     </row>
   </sheetData>
@@ -35004,13 +35004,13 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>60.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="3">
@@ -35018,13 +35018,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>29.0</v>
+        <v>33.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>52.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="4">
@@ -35038,7 +35038,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>82.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="5">
@@ -35052,7 +35052,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>89.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="6">
@@ -35066,7 +35066,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>101.0</v>
+        <v>69.0</v>
       </c>
     </row>
   </sheetData>
@@ -35105,7 +35105,7 @@
         <v>46.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="3">
@@ -35113,7 +35113,7 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>35.0</v>
+        <v>40.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
@@ -35133,7 +35133,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>45.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="5">
@@ -35147,7 +35147,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>50.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="6">
@@ -35161,7 +35161,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>54.0</v>
+        <v>47.0</v>
       </c>
     </row>
   </sheetData>
@@ -35289,7 +35289,7 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>40.0</v>
@@ -35303,13 +35303,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>50.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="4">
@@ -35323,7 +35323,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>45.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="5">
@@ -35337,7 +35337,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>63.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="6">
@@ -35351,7 +35351,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>64.0</v>
+        <v>60.0</v>
       </c>
     </row>
   </sheetData>
@@ -35390,7 +35390,7 @@
         <v>21.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="3">
@@ -35398,13 +35398,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="4">
@@ -35418,7 +35418,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>24.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="5">
@@ -35432,7 +35432,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>26.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="6">
@@ -35446,7 +35446,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>29.0</v>
+        <v>22.0</v>
       </c>
     </row>
   </sheetData>
@@ -35485,7 +35485,7 @@
         <v>15.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="3">
@@ -35493,13 +35493,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>14.0</v>
+        <v>33.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="4">
@@ -35513,7 +35513,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>13.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="5">
@@ -35527,7 +35527,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="6">
@@ -35541,7 +35541,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
     </row>
   </sheetData>
@@ -35574,13 +35574,13 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>79.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>33.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="3">
@@ -35588,13 +35588,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>44.0</v>
+        <v>37.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>104.0</v>
+        <v>83.0</v>
       </c>
     </row>
     <row r="4">
@@ -35608,7 +35608,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>113.0</v>
+        <v>107.0</v>
       </c>
     </row>
     <row r="5">
@@ -35622,7 +35622,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>123.0</v>
+        <v>116.0</v>
       </c>
     </row>
     <row r="6">
@@ -35636,7 +35636,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>135.0</v>
+        <v>127.0</v>
       </c>
     </row>
   </sheetData>
@@ -35669,13 +35669,13 @@
         <v>0.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>42.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>34.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="3">
@@ -35683,13 +35683,13 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>33.0</v>
+        <v>29.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>45.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="4">
@@ -35703,7 +35703,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="5">
@@ -35717,7 +35717,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>49.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="6">
@@ -35731,7 +35731,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>51.0</v>
+        <v>54.0</v>
       </c>
     </row>
   </sheetData>

--- a/detailed_projection_report.xlsx
+++ b/detailed_projection_report.xlsx
@@ -296,16 +296,16 @@
                 <c:v>31</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>310</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>196</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>52</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>253</c:v>
+                <c:v>314</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>199</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>53</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>256</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -995,19 +995,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>11</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>78</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>58</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>73</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>84</c:v>
+                <c:v>12</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>81</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>61</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>76</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>88</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -1937,10 +1937,10 @@
                 <c:v>15</c:v>
               </c:pt>
               <c:pt idx="2">
-                <c:v>17</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>19</c:v>
+                <c:v>18</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>20</c:v>
               </c:pt>
               <c:pt idx="4">
                 <c:v>22</c:v>
@@ -2870,16 +2870,16 @@
                 <c:v>12</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>111</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>82</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>89</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>144</c:v>
+                <c:v>116</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>86</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>93</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>151</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -3338,16 +3338,16 @@
                 <c:v>24</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>199</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>164</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>174</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>218</c:v>
+                <c:v>206</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>170</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>180</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>226</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -3803,19 +3803,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>14</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>57</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>58</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>49</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>72</c:v>
+                <c:v>15</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>59</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>60</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>51</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>75</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -4274,16 +4274,16 @@
                 <c:v>44</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>29</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>26</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>22</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>51</c:v>
+                <c:v>31</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>27</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>24</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>54</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -4508,16 +4508,16 @@
                 <c:v>21</c:v>
               </c:pt>
               <c:pt idx="1">
+                <c:v>113</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>109</c:v>
+              </c:pt>
+              <c:pt idx="3">
                 <c:v>110</c:v>
               </c:pt>
-              <c:pt idx="2">
-                <c:v>106</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>107</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>125</c:v>
+              <c:pt idx="4">
+                <c:v>128</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -5210,16 +5210,16 @@
                 <c:v>4</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>52</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>50</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>60</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>83</c:v>
+                <c:v>56</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>53</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>63</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>88</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -5909,19 +5909,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>27</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>48</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>30</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>37</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>51</c:v>
+                <c:v>28</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>50</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>31</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>38</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>53</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -6848,16 +6848,16 @@
                 <c:v>3</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>34</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>22</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>11</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>30</c:v>
+                <c:v>37</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>24</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>12</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>33</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -7316,16 +7316,16 @@
                 <c:v>42</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>262</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>209</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>221</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>307</c:v>
+                <c:v>265</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>212</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>224</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>310</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -7550,16 +7550,16 @@
                 <c:v>9</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>97</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>67</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>101</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>101</c:v>
+                <c:v>103</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>71</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>107</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>107</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -7781,19 +7781,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>27</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>59</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>46</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>16</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>50</c:v>
+                <c:v>28</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>62</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>49</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>17</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>53</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -8489,13 +8489,13 @@
                 <c:v>23</c:v>
               </c:pt>
               <c:pt idx="2">
-                <c:v>20</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>27</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>31</c:v>
+                <c:v>21</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>28</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>32</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -8720,16 +8720,16 @@
                 <c:v>8</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>66</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>47</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>60</c:v>
-              </c:pt>
-              <c:pt idx="4">
                 <c:v>68</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>48</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>62</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>70</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -9653,19 +9653,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>3</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>36</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>28</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>70</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>56</c:v>
+                <c:v>4</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>39</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>30</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>75</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>60</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -9887,19 +9887,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>12</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>86</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>73</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>80</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>93</c:v>
+                <c:v>13</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>87</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>74</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>81</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>94</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -10358,16 +10358,16 @@
                 <c:v>22</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>213</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>167</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>219</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>279</c:v>
+                <c:v>220</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>172</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>226</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>288</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -10589,19 +10589,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>42</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>145</c:v>
-              </c:pt>
-              <c:pt idx="2">
+                <c:v>43</c:v>
+              </c:pt>
+              <c:pt idx="1">
                 <c:v>149</c:v>
               </c:pt>
-              <c:pt idx="3">
-                <c:v>160</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>175</c:v>
+              <c:pt idx="2">
+                <c:v>152</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>164</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>179</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -11057,19 +11057,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>10</c:v>
-              </c:pt>
-              <c:pt idx="1">
+                <c:v>11</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>41</c:v>
+              </c:pt>
+              <c:pt idx="2">
                 <c:v>40</c:v>
               </c:pt>
-              <c:pt idx="2">
-                <c:v>39</c:v>
-              </c:pt>
               <c:pt idx="3">
                 <c:v>38</c:v>
               </c:pt>
               <c:pt idx="4">
-                <c:v>51</c:v>
+                <c:v>52</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -11294,16 +11294,16 @@
                 <c:v>2</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>39</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>53</c:v>
-              </c:pt>
-              <c:pt idx="3">
+                <c:v>36</c:v>
+              </c:pt>
+              <c:pt idx="2">
                 <c:v>49</c:v>
               </c:pt>
-              <c:pt idx="4">
-                <c:v>53</c:v>
+              <c:pt idx="3">
+                <c:v>45</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>49</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -11759,19 +11759,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>29</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>83</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>107</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>116</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>127</c:v>
+                <c:v>30</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>85</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>110</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>119</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>131</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -12464,16 +12464,16 @@
                 <c:v>13</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>70</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>50</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>62</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>83</c:v>
+                <c:v>73</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>52</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>64</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>86</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -13172,10 +13172,10 @@
                 <c:v>5</c:v>
               </c:pt>
               <c:pt idx="3">
-                <c:v>3</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>8</c:v>
+                <c:v>5</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>15</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -13400,16 +13400,16 @@
                 <c:v>6</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>32</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>25</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>38</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>31</c:v>
+                <c:v>35</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>27</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>41</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>33</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -13634,16 +13634,16 @@
                 <c:v>3</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>34</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>22</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>11</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>30</c:v>
+                <c:v>37</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>24</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>12</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>33</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -13868,16 +13868,16 @@
                 <c:v>9</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>97</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>67</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>101</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>101</c:v>
+                <c:v>103</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>71</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>107</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>107</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -14099,19 +14099,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>4</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>7</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>27</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>77</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>107</c:v>
+                <c:v>5</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>9</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>34</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>96</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>134</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -14804,16 +14804,16 @@
                 <c:v>32</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>179</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>150</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>139</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>214</c:v>
+                <c:v>181</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>151</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>140</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>217</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -15983,7 +15983,7 @@
                 <c:v>2</c:v>
               </c:pt>
               <c:pt idx="4">
-                <c:v>3</c:v>
+                <c:v>4</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -16205,19 +16205,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>38</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>42</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>56</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>53</c:v>
-              </c:pt>
-              <c:pt idx="4">
+                <c:v>37</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>41</c:v>
+              </c:pt>
+              <c:pt idx="2">
                 <c:v>54</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>51</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>52</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -16439,19 +16439,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>24</c:v>
-              </c:pt>
-              <c:pt idx="1">
+                <c:v>26</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>48</c:v>
+              </c:pt>
+              <c:pt idx="2">
                 <c:v>45</c:v>
               </c:pt>
-              <c:pt idx="2">
-                <c:v>42</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>58</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>60</c:v>
+              <c:pt idx="3">
+                <c:v>63</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>64</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -17141,19 +17141,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>29</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>33</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>39</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>44</c:v>
-              </c:pt>
-              <c:pt idx="4">
+                <c:v>28</c:v>
+              </c:pt>
+              <c:pt idx="1">
                 <c:v>32</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>38</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>43</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>31</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -17378,16 +17378,16 @@
                 <c:v>11</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>103</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>84</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>88</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>97</c:v>
+                <c:v>105</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>86</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>90</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>99</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -17846,16 +17846,16 @@
                 <c:v>4</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>39</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>30</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>28</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>44</c:v>
+                <c:v>40</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>31</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>29</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>45</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -18782,16 +18782,16 @@
                 <c:v>9</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>226</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>212</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>228</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>368</c:v>
+                <c:v>237</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>222</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>239</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>386</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -19016,16 +19016,16 @@
                 <c:v>9</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>65</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>45</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>55</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>64</c:v>
+                <c:v>67</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>46</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>57</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>66</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -19250,16 +19250,16 @@
                 <c:v>9</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>55</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>48</c:v>
-              </c:pt>
-              <c:pt idx="3">
+                <c:v>56</c:v>
+              </c:pt>
+              <c:pt idx="2">
                 <c:v>49</c:v>
               </c:pt>
-              <c:pt idx="4">
-                <c:v>65</c:v>
+              <c:pt idx="3">
+                <c:v>50</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>67</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -20654,16 +20654,16 @@
                 <c:v>6</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>32</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>25</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>38</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>31</c:v>
+                <c:v>35</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>27</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>41</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>33</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -21122,16 +21122,16 @@
                 <c:v>5</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>40</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>56</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>60</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>69</c:v>
+                <c:v>42</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>58</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>63</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>72</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -21365,7 +21365,7 @@
                 <c:v>44</c:v>
               </c:pt>
               <c:pt idx="4">
-                <c:v>47</c:v>
+                <c:v>48</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -21821,19 +21821,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>24</c:v>
-              </c:pt>
-              <c:pt idx="1">
+                <c:v>26</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>48</c:v>
+              </c:pt>
+              <c:pt idx="2">
                 <c:v>45</c:v>
               </c:pt>
-              <c:pt idx="2">
-                <c:v>42</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>58</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>60</c:v>
+              <c:pt idx="3">
+                <c:v>63</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>64</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -22061,10 +22061,10 @@
                 <c:v>15</c:v>
               </c:pt>
               <c:pt idx="2">
-                <c:v>17</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>19</c:v>
+                <c:v>18</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>20</c:v>
               </c:pt>
               <c:pt idx="4">
                 <c:v>22</c:v>
@@ -22523,19 +22523,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>29</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>83</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>107</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>116</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>127</c:v>
+                <c:v>30</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>85</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>110</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>119</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>131</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -22757,19 +22757,19 @@
             <c:numLit>
               <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>38</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>42</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>56</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>53</c:v>
-              </c:pt>
-              <c:pt idx="4">
+                <c:v>37</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>41</c:v>
+              </c:pt>
+              <c:pt idx="2">
                 <c:v>54</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>51</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>52</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
@@ -26569,7 +26569,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>310.0</v>
+        <v>314.0</v>
       </c>
     </row>
     <row r="4">
@@ -26583,7 +26583,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>196.0</v>
+        <v>199.0</v>
       </c>
     </row>
     <row r="5">
@@ -26597,7 +26597,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="6">
@@ -26611,7 +26611,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>253.0</v>
+        <v>256.0</v>
       </c>
     </row>
   </sheetData>
@@ -26840,7 +26840,7 @@
         <v>86.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="3">
@@ -26854,7 +26854,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>78.0</v>
+        <v>81.0</v>
       </c>
     </row>
     <row r="4">
@@ -26868,7 +26868,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>58.0</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="5">
@@ -26882,7 +26882,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>73.0</v>
+        <v>76.0</v>
       </c>
     </row>
     <row r="6">
@@ -26896,7 +26896,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>84.0</v>
+        <v>88.0</v>
       </c>
     </row>
   </sheetData>
@@ -27248,7 +27248,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="5">
@@ -27262,7 +27262,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="6">
@@ -27614,7 +27614,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>111.0</v>
+        <v>116.0</v>
       </c>
     </row>
     <row r="4">
@@ -27628,7 +27628,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>82.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="5">
@@ -27642,7 +27642,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>89.0</v>
+        <v>93.0</v>
       </c>
     </row>
     <row r="6">
@@ -27656,7 +27656,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>144.0</v>
+        <v>151.0</v>
       </c>
     </row>
   </sheetData>
@@ -27804,7 +27804,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>199.0</v>
+        <v>206.0</v>
       </c>
     </row>
     <row r="4">
@@ -27818,7 +27818,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>164.0</v>
+        <v>170.0</v>
       </c>
     </row>
     <row r="5">
@@ -27832,7 +27832,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>174.0</v>
+        <v>180.0</v>
       </c>
     </row>
     <row r="6">
@@ -27846,7 +27846,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>218.0</v>
+        <v>226.0</v>
       </c>
     </row>
   </sheetData>
@@ -27980,7 +27980,7 @@
         <v>69.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="3">
@@ -27994,7 +27994,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>57.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="4">
@@ -28008,7 +28008,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>58.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="5">
@@ -28022,7 +28022,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>49.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="6">
@@ -28036,7 +28036,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>72.0</v>
+        <v>75.0</v>
       </c>
     </row>
   </sheetData>
@@ -28184,7 +28184,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="4">
@@ -28198,7 +28198,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="5">
@@ -28212,7 +28212,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="6">
@@ -28226,7 +28226,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>51.0</v>
+        <v>54.0</v>
       </c>
     </row>
   </sheetData>
@@ -28279,7 +28279,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>110.0</v>
+        <v>113.0</v>
       </c>
     </row>
     <row r="4">
@@ -28293,7 +28293,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>106.0</v>
+        <v>109.0</v>
       </c>
     </row>
     <row r="5">
@@ -28307,7 +28307,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>107.0</v>
+        <v>110.0</v>
       </c>
     </row>
     <row r="6">
@@ -28321,7 +28321,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>125.0</v>
+        <v>128.0</v>
       </c>
     </row>
   </sheetData>
@@ -28564,7 +28564,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="4">
@@ -28578,7 +28578,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>50.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="5">
@@ -28592,7 +28592,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>60.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="6">
@@ -28606,7 +28606,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>83.0</v>
+        <v>88.0</v>
       </c>
     </row>
   </sheetData>
@@ -28835,7 +28835,7 @@
         <v>47.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="3">
@@ -28849,7 +28849,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>48.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="4">
@@ -28863,7 +28863,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="5">
@@ -28877,7 +28877,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="6">
@@ -28891,7 +28891,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>51.0</v>
+        <v>53.0</v>
       </c>
     </row>
   </sheetData>
@@ -29229,7 +29229,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>34.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="4">
@@ -29243,7 +29243,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="5">
@@ -29257,7 +29257,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="6">
@@ -29271,7 +29271,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>30.0</v>
+        <v>33.0</v>
       </c>
     </row>
   </sheetData>
@@ -29419,7 +29419,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>262.0</v>
+        <v>265.0</v>
       </c>
     </row>
     <row r="4">
@@ -29433,7 +29433,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>209.0</v>
+        <v>212.0</v>
       </c>
     </row>
     <row r="5">
@@ -29447,7 +29447,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>221.0</v>
+        <v>224.0</v>
       </c>
     </row>
     <row r="6">
@@ -29461,7 +29461,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>307.0</v>
+        <v>310.0</v>
       </c>
     </row>
   </sheetData>
@@ -29514,7 +29514,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>97.0</v>
+        <v>103.0</v>
       </c>
     </row>
     <row r="4">
@@ -29528,7 +29528,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="5">
@@ -29542,7 +29542,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>101.0</v>
+        <v>107.0</v>
       </c>
     </row>
     <row r="6">
@@ -29556,7 +29556,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>101.0</v>
+        <v>107.0</v>
       </c>
     </row>
   </sheetData>
@@ -29595,7 +29595,7 @@
         <v>49.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="3">
@@ -29609,7 +29609,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>59.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="4">
@@ -29623,7 +29623,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>46.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="5">
@@ -29637,7 +29637,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="6">
@@ -29651,7 +29651,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>50.0</v>
+        <v>53.0</v>
       </c>
     </row>
   </sheetData>
@@ -29908,7 +29908,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="5">
@@ -29922,7 +29922,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="6">
@@ -29936,7 +29936,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
   </sheetData>
@@ -29989,7 +29989,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>66.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="4">
@@ -30003,7 +30003,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="5">
@@ -30017,7 +30017,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>60.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="6">
@@ -30031,7 +30031,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>68.0</v>
+        <v>70.0</v>
       </c>
     </row>
   </sheetData>
@@ -30355,7 +30355,7 @@
         <v>60.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="3">
@@ -30369,7 +30369,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>36.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="4">
@@ -30383,7 +30383,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="5">
@@ -30397,7 +30397,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>70.0</v>
+        <v>75.0</v>
       </c>
     </row>
     <row r="6">
@@ -30411,7 +30411,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>56.0</v>
+        <v>60.0</v>
       </c>
     </row>
   </sheetData>
@@ -30450,7 +30450,7 @@
         <v>91.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="3">
@@ -30464,7 +30464,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>86.0</v>
+        <v>87.0</v>
       </c>
     </row>
     <row r="4">
@@ -30478,7 +30478,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>73.0</v>
+        <v>74.0</v>
       </c>
     </row>
     <row r="5">
@@ -30492,7 +30492,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>80.0</v>
+        <v>81.0</v>
       </c>
     </row>
     <row r="6">
@@ -30506,7 +30506,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
     </row>
   </sheetData>
@@ -30654,7 +30654,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>213.0</v>
+        <v>220.0</v>
       </c>
     </row>
     <row r="4">
@@ -30668,7 +30668,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>167.0</v>
+        <v>172.0</v>
       </c>
     </row>
     <row r="5">
@@ -30682,7 +30682,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>219.0</v>
+        <v>226.0</v>
       </c>
     </row>
     <row r="6">
@@ -30696,7 +30696,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>279.0</v>
+        <v>288.0</v>
       </c>
     </row>
   </sheetData>
@@ -30735,7 +30735,7 @@
         <v>152.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>42.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="3">
@@ -30749,7 +30749,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>145.0</v>
+        <v>149.0</v>
       </c>
     </row>
     <row r="4">
@@ -30763,7 +30763,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>149.0</v>
+        <v>152.0</v>
       </c>
     </row>
     <row r="5">
@@ -30777,7 +30777,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>160.0</v>
+        <v>164.0</v>
       </c>
     </row>
     <row r="6">
@@ -30791,7 +30791,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>175.0</v>
+        <v>179.0</v>
       </c>
     </row>
   </sheetData>
@@ -30925,7 +30925,7 @@
         <v>48.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="3">
@@ -30939,7 +30939,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>40.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="4">
@@ -30953,7 +30953,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>39.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="5">
@@ -30981,7 +30981,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>51.0</v>
+        <v>52.0</v>
       </c>
     </row>
   </sheetData>
@@ -31034,7 +31034,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>39.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="4">
@@ -31048,7 +31048,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>53.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="5">
@@ -31062,7 +31062,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>49.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="6">
@@ -31076,7 +31076,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>53.0</v>
+        <v>49.0</v>
       </c>
     </row>
   </sheetData>
@@ -31210,7 +31210,7 @@
         <v>79.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="3">
@@ -31224,7 +31224,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>83.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="4">
@@ -31238,7 +31238,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>107.0</v>
+        <v>110.0</v>
       </c>
     </row>
     <row r="5">
@@ -31252,7 +31252,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>116.0</v>
+        <v>119.0</v>
       </c>
     </row>
     <row r="6">
@@ -31266,7 +31266,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>127.0</v>
+        <v>131.0</v>
       </c>
     </row>
   </sheetData>
@@ -31509,7 +31509,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>70.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="4">
@@ -31523,7 +31523,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>50.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="5">
@@ -31537,7 +31537,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>62.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="6">
@@ -31551,7 +31551,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>83.0</v>
+        <v>86.0</v>
       </c>
     </row>
   </sheetData>
@@ -31822,7 +31822,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="6">
@@ -31836,7 +31836,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>8.0</v>
+        <v>15.0</v>
       </c>
     </row>
   </sheetData>
@@ -31889,7 +31889,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="4">
@@ -31903,7 +31903,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="5">
@@ -31917,7 +31917,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>38.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="6">
@@ -31931,7 +31931,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
     </row>
   </sheetData>
@@ -31984,7 +31984,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>34.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="4">
@@ -31998,7 +31998,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="5">
@@ -32012,7 +32012,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="6">
@@ -32026,7 +32026,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>30.0</v>
+        <v>33.0</v>
       </c>
     </row>
   </sheetData>
@@ -32079,7 +32079,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>97.0</v>
+        <v>103.0</v>
       </c>
     </row>
     <row r="4">
@@ -32093,7 +32093,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="5">
@@ -32107,7 +32107,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>101.0</v>
+        <v>107.0</v>
       </c>
     </row>
     <row r="6">
@@ -32121,7 +32121,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>101.0</v>
+        <v>107.0</v>
       </c>
     </row>
   </sheetData>
@@ -32160,7 +32160,7 @@
         <v>49.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="3">
@@ -32174,7 +32174,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="4">
@@ -32188,7 +32188,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>27.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="5">
@@ -32202,7 +32202,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>77.0</v>
+        <v>96.0</v>
       </c>
     </row>
     <row r="6">
@@ -32216,7 +32216,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>107.0</v>
+        <v>134.0</v>
       </c>
     </row>
   </sheetData>
@@ -32459,7 +32459,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>179.0</v>
+        <v>181.0</v>
       </c>
     </row>
     <row r="4">
@@ -32473,7 +32473,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>150.0</v>
+        <v>151.0</v>
       </c>
     </row>
     <row r="5">
@@ -32487,7 +32487,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>139.0</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="6">
@@ -32501,7 +32501,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>214.0</v>
+        <v>217.0</v>
       </c>
     </row>
   </sheetData>
@@ -32976,7 +32976,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
   </sheetData>
@@ -33015,7 +33015,7 @@
         <v>42.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>38.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="3">
@@ -33029,7 +33029,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>42.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="4">
@@ -33043,7 +33043,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>56.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="5">
@@ -33057,7 +33057,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>53.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="6">
@@ -33071,7 +33071,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
   </sheetData>
@@ -33110,7 +33110,7 @@
         <v>40.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>24.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="3">
@@ -33124,7 +33124,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="4">
@@ -33138,7 +33138,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>42.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="5">
@@ -33152,7 +33152,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>58.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="6">
@@ -33166,7 +33166,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>60.0</v>
+        <v>64.0</v>
       </c>
     </row>
   </sheetData>
@@ -33395,7 +33395,7 @@
         <v>31.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="3">
@@ -33409,7 +33409,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>33.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="4">
@@ -33423,7 +33423,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>39.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="5">
@@ -33437,7 +33437,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>44.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="6">
@@ -33451,7 +33451,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
     </row>
   </sheetData>
@@ -33504,7 +33504,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>103.0</v>
+        <v>105.0</v>
       </c>
     </row>
     <row r="4">
@@ -33518,7 +33518,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>84.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="5">
@@ -33532,7 +33532,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>88.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="6">
@@ -33546,7 +33546,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>97.0</v>
+        <v>99.0</v>
       </c>
     </row>
   </sheetData>
@@ -33694,7 +33694,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>39.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="4">
@@ -33708,7 +33708,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="5">
@@ -33722,7 +33722,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="6">
@@ -33736,7 +33736,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>44.0</v>
+        <v>45.0</v>
       </c>
     </row>
   </sheetData>
@@ -34074,7 +34074,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>226.0</v>
+        <v>237.0</v>
       </c>
     </row>
     <row r="4">
@@ -34088,7 +34088,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>212.0</v>
+        <v>222.0</v>
       </c>
     </row>
     <row r="5">
@@ -34102,7 +34102,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>228.0</v>
+        <v>239.0</v>
       </c>
     </row>
     <row r="6">
@@ -34116,7 +34116,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>368.0</v>
+        <v>386.0</v>
       </c>
     </row>
   </sheetData>
@@ -34169,7 +34169,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="4">
@@ -34183,7 +34183,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>45.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="5">
@@ -34197,7 +34197,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>55.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="6">
@@ -34211,7 +34211,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>64.0</v>
+        <v>66.0</v>
       </c>
     </row>
   </sheetData>
@@ -34264,7 +34264,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>55.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="4">
@@ -34278,7 +34278,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="5">
@@ -34292,7 +34292,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>49.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="6">
@@ -34306,7 +34306,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
   </sheetData>
@@ -34834,7 +34834,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="4">
@@ -34848,7 +34848,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="5">
@@ -34862,7 +34862,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>38.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="6">
@@ -34876,7 +34876,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
     </row>
   </sheetData>
@@ -35024,7 +35024,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>40.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="4">
@@ -35038,7 +35038,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>56.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="5">
@@ -35052,7 +35052,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>60.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="6">
@@ -35066,7 +35066,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>69.0</v>
+        <v>72.0</v>
       </c>
     </row>
   </sheetData>
@@ -35161,7 +35161,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
   </sheetData>
@@ -35295,7 +35295,7 @@
         <v>40.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>24.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="3">
@@ -35309,7 +35309,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="4">
@@ -35323,7 +35323,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>42.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="5">
@@ -35337,7 +35337,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>58.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="6">
@@ -35351,7 +35351,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>60.0</v>
+        <v>64.0</v>
       </c>
     </row>
   </sheetData>
@@ -35418,7 +35418,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="5">
@@ -35432,7 +35432,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="6">
@@ -35580,7 +35580,7 @@
         <v>79.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="3">
@@ -35594,7 +35594,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>83.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="4">
@@ -35608,7 +35608,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>107.0</v>
+        <v>110.0</v>
       </c>
     </row>
     <row r="5">
@@ -35622,7 +35622,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>116.0</v>
+        <v>119.0</v>
       </c>
     </row>
     <row r="6">
@@ -35636,7 +35636,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>127.0</v>
+        <v>131.0</v>
       </c>
     </row>
   </sheetData>
@@ -35675,7 +35675,7 @@
         <v>42.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>38.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="3">
@@ -35689,7 +35689,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>42.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="4">
@@ -35703,7 +35703,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>56.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="5">
@@ -35717,7 +35717,7 @@
         <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>53.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="6">
@@ -35731,7 +35731,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
   </sheetData>
